--- a/artfynd/A 30670-2025 artfynd.xlsx
+++ b/artfynd/A 30670-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>124825231</v>
       </c>
       <c r="B2" t="n">
-        <v>92514</v>
+        <v>92516</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>124825232</v>
       </c>
       <c r="B3" t="n">
-        <v>92534</v>
+        <v>92536</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 30670-2025 artfynd.xlsx
+++ b/artfynd/A 30670-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>124825231</v>
       </c>
       <c r="B2" t="n">
-        <v>92516</v>
+        <v>92518</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>124825232</v>
       </c>
       <c r="B3" t="n">
-        <v>92536</v>
+        <v>92538</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 30670-2025 artfynd.xlsx
+++ b/artfynd/A 30670-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>124825231</v>
       </c>
       <c r="B2" t="n">
-        <v>92518</v>
+        <v>92520</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>124825232</v>
       </c>
       <c r="B3" t="n">
-        <v>92538</v>
+        <v>92540</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 30670-2025 artfynd.xlsx
+++ b/artfynd/A 30670-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>124825231</v>
       </c>
       <c r="B2" t="n">
-        <v>92520</v>
+        <v>92524</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>124825232</v>
       </c>
       <c r="B3" t="n">
-        <v>92540</v>
+        <v>92544</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 30670-2025 artfynd.xlsx
+++ b/artfynd/A 30670-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>124825231</v>
       </c>
       <c r="B2" t="n">
-        <v>92524</v>
+        <v>92527</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>124825232</v>
       </c>
       <c r="B3" t="n">
-        <v>92544</v>
+        <v>92547</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
